--- a/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
+++ b/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\Passion-Lecture\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\Passion-Lecture\Doc Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F67D5BC-E8E5-4969-83D9-1EEE0EC39C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2C6111-C776-4DD9-B753-B0DFF48C2D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -143,6 +143,12 @@
   </si>
   <si>
     <t>J'ai fais le quick start</t>
+  </si>
+  <si>
+    <t>J'ai commencé le rapport</t>
+  </si>
+  <si>
+    <t>J'ai aidé mon collège pour la création du mcd</t>
   </si>
 </sst>
 </file>
@@ -1190,16 +1196,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2045,16 +2051,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.13333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1</c:v>
+                  <c:v>6.6666666666666666E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4289,7 +4295,7 @@
       <c r="B3" s="96"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>1 heures 40 minutes</v>
+        <v>3 heures 45 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4304,15 +4310,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4347,11 +4353,13 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="61" t="str">
+      <c r="A7" s="61">
         <f>IF(ISBLANK(B7),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B7))</f>
-        <v/>
-      </c>
-      <c r="B7" s="26"/>
+        <v>18</v>
+      </c>
+      <c r="B7" s="26">
+        <v>46140</v>
+      </c>
       <c r="C7" s="27">
         <v>1</v>
       </c>
@@ -4367,14 +4375,16 @@
       <c r="G7" s="38"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="str">
+      <c r="A8" s="62">
         <f>IF(ISBLANK(B8),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B8))</f>
-        <v/>
-      </c>
-      <c r="B8" s="30"/>
+        <v>18</v>
+      </c>
+      <c r="B8" s="30">
+        <v>46140</v>
+      </c>
       <c r="C8" s="31"/>
       <c r="D8" s="32">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E8" s="33" t="s">
         <v>16</v>
@@ -4394,15 +4404,25 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="63" t="str">
+      <c r="A9" s="63">
         <f>IF(ISBLANK(B9),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B9))</f>
-        <v/>
-      </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="B9" s="34">
+        <v>46140</v>
+      </c>
+      <c r="C9" s="35">
+        <v>1</v>
+      </c>
+      <c r="D9" s="36">
+        <v>30</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>34</v>
+      </c>
       <c r="G9" s="40"/>
       <c r="M9" t="s">
         <v>16</v>
@@ -4415,15 +4435,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="62" t="str">
+      <c r="A10" s="62">
         <f>IF(ISBLANK(B10),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B10))</f>
-        <v/>
-      </c>
-      <c r="B10" s="30"/>
+        <v>18</v>
+      </c>
+      <c r="B10" s="30">
+        <v>46140</v>
+      </c>
       <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="23"/>
+      <c r="D10" s="32">
+        <v>30</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>35</v>
+      </c>
       <c r="G10" s="39"/>
       <c r="M10" t="s">
         <v>18</v>
@@ -10885,11 +10913,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10897,11 +10925,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>0 h 00 min</v>
+        <v>0 h 30 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10922,11 +10950,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10934,11 +10962,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>0 h 10 min</v>
+        <v>0 h 15 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.1</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10992,15 +11020,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11008,11 +11036,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>1 h 30 min</v>
+        <v>3 h 00 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11064,26 +11092,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>1 h 40 min</v>
+        <v>3 h 45 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>1.8518518518518517E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>30</v>
@@ -11122,6 +11150,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="b4a5ad45c54fa8cfccf4b5a6490850dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fe3b3ea8edd81a9012b97c6ddf640adc" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11310,15 +11347,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11331,6 +11359,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B10C3F0-E765-401E-838F-B3E1E8C6407D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11349,14 +11385,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
+++ b/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\Passion-Lecture\Doc Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2C6111-C776-4DD9-B753-B0DFF48C2D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F800183A-5CB8-4073-BB23-F23AF7C36D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -149,6 +149,15 @@
   </si>
   <si>
     <t>J'ai aidé mon collège pour la création du mcd</t>
+  </si>
+  <si>
+    <t>J'ai écouter le profs</t>
+  </si>
+  <si>
+    <t>J'ai avancé un peu sur le rapport en attendant le mcd de mon collègue</t>
+  </si>
+  <si>
+    <t>J'ai créer tout les validators</t>
   </si>
 </sst>
 </file>
@@ -1196,16 +1205,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15</c:v>
+                  <c:v>145</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>180</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2051,16 +2060,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.13333333333333333</c:v>
+                  <c:v>0.12345679012345678</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.6666666666666666E-2</c:v>
+                  <c:v>0.35802469135802467</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.8</c:v>
+                  <c:v>0.51851851851851849</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4295,7 +4304,7 @@
       <c r="B3" s="96"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>3 heures 45 minutes</v>
+        <v>6 heures 45 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4310,15 +4319,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>225</v>
+        <v>405</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4464,15 +4473,23 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="63" t="str">
+      <c r="A11" s="63">
         <f>IF(ISBLANK(B11),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B11))</f>
-        <v/>
-      </c>
-      <c r="B11" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="B11" s="34">
+        <v>46146</v>
+      </c>
       <c r="C11" s="35"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="23"/>
+      <c r="D11" s="36">
+        <v>20</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>36</v>
+      </c>
       <c r="G11" s="40"/>
       <c r="M11" t="s">
         <v>15</v>
@@ -4485,15 +4502,23 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="62" t="str">
+      <c r="A12" s="62">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
-        <v/>
-      </c>
-      <c r="B12" s="30"/>
+        <v>19</v>
+      </c>
+      <c r="B12" s="30">
+        <v>46146</v>
+      </c>
       <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="23"/>
+      <c r="D12" s="32">
+        <v>30</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>37</v>
+      </c>
       <c r="G12" s="39"/>
       <c r="M12" t="s">
         <v>19</v>
@@ -4506,15 +4531,25 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="str">
+      <c r="A13" s="63">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="23"/>
+        <v>19</v>
+      </c>
+      <c r="B13" s="34">
+        <v>46146</v>
+      </c>
+      <c r="C13" s="35">
+        <v>2</v>
+      </c>
+      <c r="D13" s="36">
+        <v>10</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="G13" s="40"/>
       <c r="N13">
         <v>6</v>
@@ -10913,11 +10948,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10925,11 +10960,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>0 h 30 min</v>
+        <v>0 h 50 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.13333333333333333</v>
+        <v>0.12345679012345678</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10946,15 +10981,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10962,11 +10997,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>0 h 15 min</v>
+        <v>2 h 25 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.35802469135802467</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11024,11 +11059,11 @@
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11036,11 +11071,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>3 h 00 min</v>
+        <v>3 h 30 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.51851851851851849</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11092,26 +11127,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>225</v>
+        <v>405</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>3 h 45 min</v>
+        <v>6 h 45 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>4.1666666666666664E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>30</v>
@@ -11150,15 +11185,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="b4a5ad45c54fa8cfccf4b5a6490850dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fe3b3ea8edd81a9012b97c6ddf640adc" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11347,6 +11373,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11359,14 +11394,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B10C3F0-E765-401E-838F-B3E1E8C6407D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11385,6 +11412,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
+++ b/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\Passion-Lecture\Doc Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F800183A-5CB8-4073-BB23-F23AF7C36D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444F40B6-A622-40F2-ABF3-40BA22070453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -158,6 +158,21 @@
   </si>
   <si>
     <t>J'ai créer tout les validators</t>
+  </si>
+  <si>
+    <t>J'ai eu un problème avec mon ordinateur il a freez et j'ai eu un probleme avec les écrants qui étaient noir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'ai ajouter le seeder author </t>
+  </si>
+  <si>
+    <t>J'ai modifier mes validateurs car ils n'étaient pas correcte avec les mauvais noms</t>
+  </si>
+  <si>
+    <t>J'ai fais le controller author</t>
+  </si>
+  <si>
+    <t>J'ai fais les test api avec bruno</t>
   </si>
 </sst>
 </file>
@@ -1205,13 +1220,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>145</c:v>
+                  <c:v>285</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>210</c:v>
@@ -2060,16 +2075,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.12345679012345678</c:v>
+                  <c:v>0.17460317460317459</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.35802469135802467</c:v>
+                  <c:v>0.45238095238095238</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.968253968253968E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.51851851851851849</c:v>
+                  <c:v>0.33333333333333331</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4304,7 +4319,7 @@
       <c r="B3" s="96"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>6 heures 45 minutes</v>
+        <v>10 heures 30 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4319,15 +4334,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>405</v>
+        <v>630</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4558,16 +4573,26 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="62" t="str">
+    <row r="14" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="62">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
-        <v/>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="23"/>
+        <v>19</v>
+      </c>
+      <c r="B14" s="30">
+        <v>46147</v>
+      </c>
+      <c r="C14" s="31">
+        <v>1</v>
+      </c>
+      <c r="D14" s="32">
+        <v>0</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>39</v>
+      </c>
       <c r="G14" s="39"/>
       <c r="N14">
         <v>7</v>
@@ -4577,15 +4602,23 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="str">
+      <c r="A15" s="63">
         <f>IF(ISBLANK(B15),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B15))</f>
-        <v/>
-      </c>
-      <c r="B15" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="B15" s="34">
+        <v>46147</v>
+      </c>
       <c r="C15" s="35"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="23"/>
+      <c r="D15" s="36">
+        <v>30</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>40</v>
+      </c>
       <c r="G15" s="40"/>
       <c r="N15">
         <v>8</v>
@@ -4595,45 +4628,71 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="62" t="str">
+      <c r="A16" s="62">
         <f>IF(ISBLANK(B16),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B16))</f>
-        <v/>
-      </c>
-      <c r="B16" s="30"/>
+        <v>19</v>
+      </c>
+      <c r="B16" s="30">
+        <v>46147</v>
+      </c>
       <c r="C16" s="31"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="23"/>
+      <c r="D16" s="32">
+        <v>30</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="G16" s="39"/>
       <c r="O16">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="63" t="str">
+      <c r="A17" s="63">
         <f>IF(ISBLANK(B17),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="23"/>
+        <v>19</v>
+      </c>
+      <c r="B17" s="34">
+        <v>46147</v>
+      </c>
+      <c r="C17" s="35">
+        <v>1</v>
+      </c>
+      <c r="D17" s="36">
+        <v>20</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>42</v>
+      </c>
       <c r="G17" s="40"/>
       <c r="O17">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="62" t="str">
+      <c r="A18" s="62">
         <f>IF(ISBLANK(B18),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="30"/>
+        <v>19</v>
+      </c>
+      <c r="B18" s="30">
+        <v>46147</v>
+      </c>
       <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="84"/>
+      <c r="D18" s="32">
+        <v>25</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="84" t="s">
+        <v>43</v>
+      </c>
       <c r="G18" s="39"/>
       <c r="O18">
         <v>50</v>
@@ -10944,7 +11003,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
@@ -10952,7 +11011,7 @@
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10960,11 +11019,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>0 h 50 min</v>
+        <v>1 h 50 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.12345679012345678</v>
+        <v>0.17460317460317459</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10981,15 +11040,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>145</v>
+        <v>285</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10997,11 +11056,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>2 h 25 min</v>
+        <v>4 h 45 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.35802469135802467</v>
+        <v>0.45238095238095238</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11022,11 +11081,11 @@
       </c>
       <c r="B8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E8,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E8" s="76" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11034,11 +11093,11 @@
       </c>
       <c r="F8" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>0 h 00 min</v>
+        <v>0 h 25 min</v>
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.968253968253968E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11075,7 +11134,7 @@
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.51851851851851849</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11127,26 +11186,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>405</v>
+        <v>630</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>6 h 45 min</v>
+        <v>10 h 30 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>7.4999999999999997E-2</v>
+        <v>0.11666666666666667</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>30</v>
@@ -11185,6 +11244,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="b4a5ad45c54fa8cfccf4b5a6490850dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fe3b3ea8edd81a9012b97c6ddf640adc" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11373,15 +11441,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11394,6 +11453,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B10C3F0-E765-401E-838F-B3E1E8C6407D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11412,14 +11479,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
+++ b/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\Passion-Lecture\Doc Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444F40B6-A622-40F2-ABF3-40BA22070453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD5B12C-284F-48CB-A93E-B34E47A5A6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -173,6 +173,12 @@
   </si>
   <si>
     <t>J'ai fais les test api avec bruno</t>
+  </si>
+  <si>
+    <t>J'ai ajouter le controller categorie</t>
+  </si>
+  <si>
+    <t>J'ai continuer le rapport</t>
   </si>
 </sst>
 </file>
@@ -1223,13 +1229,13 @@
                   <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>285</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>210</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2075,16 +2081,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.17460317460317459</c:v>
+                  <c:v>0.1437908496732026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.45238095238095238</c:v>
+                  <c:v>0.47058823529411764</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.968253968253968E-2</c:v>
+                  <c:v>3.2679738562091505E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.33333333333333331</c:v>
+                  <c:v>0.35294117647058826</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4319,7 +4325,7 @@
       <c r="B3" s="96"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>10 heures 30 minutes</v>
+        <v>12 heures 45 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4334,15 +4340,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>630</v>
+        <v>765</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4699,30 +4705,48 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="63" t="str">
+      <c r="A19" s="63">
         <f>IF(ISBLANK(B19),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="B19" s="34">
+        <v>46153</v>
+      </c>
+      <c r="C19" s="35">
+        <v>1</v>
+      </c>
+      <c r="D19" s="36">
+        <v>15</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>44</v>
+      </c>
       <c r="G19" s="40"/>
       <c r="O19">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="62" t="str">
+      <c r="A20" s="62">
         <f>IF(ISBLANK(B20),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
+        <v>20</v>
+      </c>
+      <c r="B20" s="30">
+        <v>46153</v>
+      </c>
+      <c r="C20" s="31">
+        <v>1</v>
+      </c>
       <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="23"/>
+      <c r="E20" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>45</v>
+      </c>
       <c r="G20" s="39"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -11023,7 +11047,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.17460317460317459</v>
+        <v>0.1437908496732026</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11040,15 +11064,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11056,11 +11080,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>4 h 45 min</v>
+        <v>6 h 00 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.45238095238095238</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11097,7 +11121,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>3.968253968253968E-2</v>
+        <v>3.2679738562091505E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11114,7 +11138,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
@@ -11122,7 +11146,7 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11130,11 +11154,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>3 h 30 min</v>
+        <v>4 h 30 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11186,26 +11210,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>630</v>
+        <v>765</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>10 h 30 min</v>
+        <v>12 h 45 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.11666666666666667</v>
+        <v>0.14166666666666666</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>30</v>
@@ -11244,15 +11268,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="b4a5ad45c54fa8cfccf4b5a6490850dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fe3b3ea8edd81a9012b97c6ddf640adc" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11441,6 +11456,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11453,14 +11477,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B10C3F0-E765-401E-838F-B3E1E8C6407D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11479,6 +11495,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
+++ b/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\Passion-Lecture\Doc Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD5B12C-284F-48CB-A93E-B34E47A5A6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE4D897-E000-4411-B1DB-6E2CF50AE876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -179,6 +179,15 @@
   </si>
   <si>
     <t>J'ai continuer le rapport</t>
+  </si>
+  <si>
+    <t>J'ai analysé mon code avec le prof</t>
+  </si>
+  <si>
+    <t>J'ai ajouter la route du controller categorie</t>
+  </si>
+  <si>
+    <t>J'ai continué le rapport</t>
   </si>
 </sst>
 </file>
@@ -1226,16 +1235,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>110</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>360</c:v>
+                  <c:v>365</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>270</c:v>
+                  <c:v>470</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2081,16 +2090,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.1437908496732026</c:v>
+                  <c:v>0.13131313131313133</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.47058823529411764</c:v>
+                  <c:v>0.36868686868686867</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.2679738562091505E-2</c:v>
+                  <c:v>2.5252525252525252E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.35294117647058826</c:v>
+                  <c:v>0.47474747474747475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4325,7 +4334,7 @@
       <c r="B3" s="96"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>12 heures 45 minutes</v>
+        <v>16 heures 30 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4340,15 +4349,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>765</v>
+        <v>990</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4740,7 +4749,9 @@
       <c r="C20" s="31">
         <v>1</v>
       </c>
-      <c r="D20" s="32"/>
+      <c r="D20" s="32">
+        <v>0</v>
+      </c>
       <c r="E20" s="33" t="s">
         <v>15</v>
       </c>
@@ -4750,39 +4761,65 @@
       <c r="G20" s="39"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="63" t="str">
+      <c r="A21" s="63">
         <f>IF(ISBLANK(B21),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="34"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="34">
+        <v>46154</v>
+      </c>
       <c r="C21" s="35"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="23"/>
+      <c r="D21" s="36">
+        <v>20</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="G21" s="40"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="62" t="str">
+      <c r="A22" s="62">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="30"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="30">
+        <v>46154</v>
+      </c>
       <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="23"/>
+      <c r="D22" s="32">
+        <v>5</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="G22" s="39"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="63" t="str">
+      <c r="A23" s="63">
         <f>IF(ISBLANK(B23),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="34">
+        <v>46154</v>
+      </c>
+      <c r="C23" s="35">
+        <v>3</v>
+      </c>
+      <c r="D23" s="36">
+        <v>20</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>48</v>
+      </c>
       <c r="G23" s="40"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -11031,11 +11068,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11043,11 +11080,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>1 h 50 min</v>
+        <v>2 h 10 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.1437908496732026</v>
+        <v>0.13131313131313133</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11068,11 +11105,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11080,11 +11117,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>6 h 00 min</v>
+        <v>6 h 05 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.47058823529411764</v>
+        <v>0.36868686868686867</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11121,7 +11158,7 @@
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>3.2679738562091505E-2</v>
+        <v>2.5252525252525252E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11138,15 +11175,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>470</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11154,11 +11191,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>4 h 30 min</v>
+        <v>7 h 50 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.35294117647058826</v>
+        <v>0.47474747474747475</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11210,26 +11247,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>765</v>
+        <v>990</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>12 h 45 min</v>
+        <v>16 h 30 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.14166666666666666</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>30</v>
@@ -11268,6 +11305,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="b4a5ad45c54fa8cfccf4b5a6490850dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fe3b3ea8edd81a9012b97c6ddf640adc" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11456,15 +11502,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11477,6 +11514,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B10C3F0-E765-401E-838F-B3E1E8C6407D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11495,14 +11540,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
+++ b/Doc Backend/X-Journal-de-Travail_PeltierThomas-backend.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv03xgo\Documents\GitHub\Passion-Lecture\Doc Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE4D897-E000-4411-B1DB-6E2CF50AE876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20B643E-16EF-46B4-8AA4-FC153071E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>J'ai continué le rapport</t>
+  </si>
+  <si>
+    <t>80% avec le prof</t>
+  </si>
+  <si>
+    <t>J'ai implémenter le système de logout</t>
   </si>
 </sst>
 </file>
@@ -1235,16 +1241,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>130</c:v>
+                  <c:v>145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>365</c:v>
+                  <c:v>430</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>470</c:v>
+                  <c:v>390</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2090,16 +2096,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.13131313131313133</c:v>
+                  <c:v>0.14646464646464646</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.36868686868686867</c:v>
+                  <c:v>0.43434343434343436</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.5252525252525252E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.47474747474747475</c:v>
+                  <c:v>0.39393939393939392</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4809,10 +4815,10 @@
         <v>46154</v>
       </c>
       <c r="C23" s="35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="36">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>15</v>
@@ -4823,27 +4829,45 @@
       <c r="G23" s="40"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="62" t="str">
+      <c r="A24" s="62">
         <f>IF(ISBLANK(B24),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="30"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="30">
+        <v>46154</v>
+      </c>
       <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="23"/>
+      <c r="D24" s="32">
+        <v>15</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="G24" s="39"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="63" t="str">
+      <c r="A25" s="63">
         <f>IF(ISBLANK(B25),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="B25" s="34">
+        <v>46154</v>
+      </c>
+      <c r="C25" s="35">
+        <v>1</v>
+      </c>
+      <c r="D25" s="36">
+        <v>5</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>50</v>
+      </c>
       <c r="G25" s="40"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -11068,11 +11092,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11080,11 +11104,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>2 h 10 min</v>
+        <v>2 h 25 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.13131313131313133</v>
+        <v>0.14646464646464646</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11101,15 +11125,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>365</v>
+        <v>430</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11117,11 +11141,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>6 h 05 min</v>
+        <v>7 h 10 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.36868686868686867</v>
+        <v>0.43434343434343436</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11175,15 +11199,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>470</v>
+        <v>390</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11191,11 +11215,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>7 h 50 min</v>
+        <v>6 h 30 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.47474747474747475</v>
+        <v>0.39393939393939392</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
